--- a/incident_report_forms/025_damage_report_for_common_areas--incident_report_forms.xlsx
+++ b/incident_report_forms/025_damage_report_for_common_areas--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,14 +531,14 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Incident Details</t>
+          <t>Damage Location</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Photos</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tenant Information</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Property Manager</t>
+          <t>Photos Count</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Damage Location</t>
+          <t>Tenant Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Tenant Contact</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Photos Count</t>
+          <t>Property Manager</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Photos</t>
+          <t>Damage Cause</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tenant Name</t>
+          <t>Damage Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,310 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tenant Contact</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tenant Contact</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tenant Contact</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Property Manager</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Property Manager</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Property Manager</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Property Manager</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Damage Report</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Damage Report</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Damage Report</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Damage Report</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Damage Report</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Damage Report</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,85 +827,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_6_choices</t>
+          <t>damage_report_for_common_areas_page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'kitchen',_'value':_'kitchen'}</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Kitchen', 'value': 'kitchen'}</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_6_choices</t>
+          <t>damage_report_for_common_areas_page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'living_room',_'value':_'living_room'}</t>
+          <t>living_room</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Living room', 'value': 'living_room'}</t>
+          <t>Living Room</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_6_choices</t>
+          <t>damage_report_for_common_areas_page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'bedroom',_'value':_'bedroom'}</t>
+          <t>bedroom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Bedroom', 'value': 'bedroom'}</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_6_choices</t>
+          <t>damage_report_for_common_areas_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'bathroom',_'value':_'bathroom'}</t>
+          <t>bathroom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Bathroom', 'value': 'bathroom'}</t>
+          <t>Bathroom</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_6_choices</t>
+          <t>damage_report_for_common_areas_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'hallway',_'value':_'hallway'}</t>
+          <t>hallway</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Hallway', 'value': 'hallway'}</t>
+          <t>Hallway</t>
         </is>
       </c>
     </row>
@@ -1216,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1',_'value':_'1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1', 'value': '1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1233,148 +934,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2',_'value':_'2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2', 'value': '2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_10_choices</t>
+          <t>damage_report_for_common_areas_page_11_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3',_'value':_'3'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3', 'value': '3'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_10_choices</t>
+          <t>damage_report_for_common_areas_page_11_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'4',_'value':_'4'}</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '4', 'value': '4'}</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>damage_report_for_common_areas_page_10_choices</t>
+          <t>damage_report_for_common_areas_page_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'5',_'value':_'5'}</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '5', 'value': '5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'yes',_'value':_'yes'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'Yes', 'value': 'yes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'no',_'value':_'no'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'No', 'value': 'no'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_'water',_'value':_'water'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': 'Water', 'value': 'water'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'fire',_'value':_'fire'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': 'Fire', 'value': 'fire'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>damage_report_for_common_areas_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'wind',_'value':_'wind'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Wind', 'value': 'wind'}</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
